--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/commodity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A1491C-4A7A-BE42-B165-44A2DBCF21F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEBAF5A-347F-3D4D-8956-0144FE8B6C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2163"/>
+  <dimension ref="A1:B2164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -17755,6 +17755,14 @@
       </c>
       <c r="B2163" s="7">
         <v>104900</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:2">
+      <c r="A2164" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B2164" s="7">
+        <v>111900</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BCCFFB-DCD1-43C3-8C48-B9330941AC84}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894BD636-7AD1-458E-8D3A-7614F38BC517}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17985" yWindow="780" windowWidth="18015" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="13">
   <si>
     <t>Lithium</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -497,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2168"/>
+  <dimension ref="A1:E2170"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="13" bestFit="1" customWidth="1"/>
@@ -37362,6 +37362,40 @@
       </c>
       <c r="E2168" s="10">
         <v>119500</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2169" s="13">
+        <v>46028</v>
+      </c>
+      <c r="B2169" s="15">
+        <v>46028</v>
+      </c>
+      <c r="C2169" s="8">
+        <v>0.625</v>
+      </c>
+      <c r="D2169" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2169" s="10">
+        <v>127500</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2170" s="13">
+        <v>46029</v>
+      </c>
+      <c r="B2170" s="15">
+        <v>46029</v>
+      </c>
+      <c r="C2170" s="8">
+        <v>0.625</v>
+      </c>
+      <c r="D2170" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2170" s="10">
+        <v>133500</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894BD636-7AD1-458E-8D3A-7614F38BC517}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29B39C6-407B-4C5A-BD26-CE1A67727C56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17985" yWindow="780" windowWidth="18015" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="13">
   <si>
     <t>Lithium</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -497,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2170"/>
+  <dimension ref="A1:E2171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="13" bestFit="1" customWidth="1"/>
@@ -37396,6 +37396,23 @@
       </c>
       <c r="E2170" s="10">
         <v>133500</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2171" s="13">
+        <v>46030</v>
+      </c>
+      <c r="B2171" s="15">
+        <v>46030</v>
+      </c>
+      <c r="C2171" s="8">
+        <v>0.625</v>
+      </c>
+      <c r="D2171" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2171" s="10">
+        <v>138500</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DCBFF3-0A7F-4A7E-92DD-4322F500908C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE3EBA5-0E31-44CD-AD8C-468EAC34A15E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27900" yWindow="1545" windowWidth="18015" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -100,8 +100,8 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -211,23 +211,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14428,7 +14428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2193"/>
+  <dimension ref="A1:H2198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.125" style="3" bestFit="1" customWidth="1"/>
@@ -58766,6 +58766,136 @@
       </c>
       <c r="H2193" s="10">
         <v>143750</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2194" s="3">
+        <v>46077</v>
+      </c>
+      <c r="B2194" s="3">
+        <v>46077</v>
+      </c>
+      <c r="C2194" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2194" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2194" s="16">
+        <v>152000</v>
+      </c>
+      <c r="F2194" s="16">
+        <v>158000</v>
+      </c>
+      <c r="G2194" s="16">
+        <v>146000</v>
+      </c>
+      <c r="H2194" s="10">
+        <v>152000</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2195" s="3">
+        <v>46078</v>
+      </c>
+      <c r="B2195" s="3">
+        <v>46078</v>
+      </c>
+      <c r="C2195" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2195" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2195" s="16">
+        <v>161750</v>
+      </c>
+      <c r="F2195" s="16">
+        <v>165500</v>
+      </c>
+      <c r="G2195" s="16">
+        <v>151970</v>
+      </c>
+      <c r="H2195" s="10">
+        <v>161750</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2196" s="3">
+        <v>46079</v>
+      </c>
+      <c r="B2196" s="3">
+        <v>46079</v>
+      </c>
+      <c r="C2196" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2196" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2196" s="16">
+        <v>173000</v>
+      </c>
+      <c r="F2196" s="16">
+        <v>178000</v>
+      </c>
+      <c r="G2196" s="16">
+        <v>161718</v>
+      </c>
+      <c r="H2196" s="10">
+        <v>173000</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2197" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B2197" s="3">
+        <v>46080</v>
+      </c>
+      <c r="C2197" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2197" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2197" s="16">
+        <v>172000</v>
+      </c>
+      <c r="F2197" s="16">
+        <v>176000</v>
+      </c>
+      <c r="G2197" s="16">
+        <v>168000</v>
+      </c>
+      <c r="H2197" s="10">
+        <v>172000</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2198" s="3">
+        <v>46083</v>
+      </c>
+      <c r="B2198" s="3">
+        <v>46083</v>
+      </c>
+      <c r="C2198" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2198" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2198" s="16">
+        <v>172500</v>
+      </c>
+      <c r="F2198" s="16">
+        <v>176000</v>
+      </c>
+      <c r="G2198" s="16">
+        <v>169000</v>
+      </c>
+      <c r="H2198" s="10">
+        <v>172500</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE3EBA5-0E31-44CD-AD8C-468EAC34A15E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD385DFF-728A-4E31-96BC-799A71F909F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27900" yWindow="1545" windowWidth="18015" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -14428,7 +14428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2198"/>
+  <dimension ref="A1:H2203"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.125" style="3" bestFit="1" customWidth="1"/>
@@ -58896,6 +58896,136 @@
       </c>
       <c r="H2198" s="10">
         <v>172500</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2199" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B2199" s="3">
+        <v>46084</v>
+      </c>
+      <c r="C2199" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2199" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2199" s="16">
+        <v>161000</v>
+      </c>
+      <c r="F2199" s="16">
+        <v>172535</v>
+      </c>
+      <c r="G2199" s="16">
+        <v>153000</v>
+      </c>
+      <c r="H2199" s="10">
+        <v>161000</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2200" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B2200" s="3">
+        <v>46085</v>
+      </c>
+      <c r="C2200" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2200" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2200" s="16">
+        <v>154000</v>
+      </c>
+      <c r="F2200" s="16">
+        <v>161032</v>
+      </c>
+      <c r="G2200" s="16">
+        <v>148000</v>
+      </c>
+      <c r="H2200" s="10">
+        <v>154000</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2201" s="3">
+        <v>46086</v>
+      </c>
+      <c r="B2201" s="3">
+        <v>46086</v>
+      </c>
+      <c r="C2201" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2201" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2201" s="16">
+        <v>156000</v>
+      </c>
+      <c r="F2201" s="16">
+        <v>160000</v>
+      </c>
+      <c r="G2201" s="16">
+        <v>152000</v>
+      </c>
+      <c r="H2201" s="10">
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2202" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B2202" s="3">
+        <v>46087</v>
+      </c>
+      <c r="C2202" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2202" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2202" s="16">
+        <v>155250</v>
+      </c>
+      <c r="F2202" s="16">
+        <v>160000</v>
+      </c>
+      <c r="G2202" s="16">
+        <v>150500</v>
+      </c>
+      <c r="H2202" s="10">
+        <v>155250</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2203" s="3">
+        <v>46090</v>
+      </c>
+      <c r="B2203" s="9">
+        <v>46090</v>
+      </c>
+      <c r="C2203" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2203" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2203" s="16">
+        <v>154750</v>
+      </c>
+      <c r="F2203" s="16">
+        <v>159500</v>
+      </c>
+      <c r="G2203" s="16">
+        <v>150000</v>
+      </c>
+      <c r="H2203" s="10">
+        <v>154750</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD385DFF-728A-4E31-96BC-799A71F909F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8EF842-96BA-47EE-994A-55ADACB5E13F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27900" yWindow="1545" windowWidth="18015" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -289,10 +289,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Lithium!$B$2:$B$2177</c:f>
+              <c:f>Lithium!$B$2:$B$12177</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="2176"/>
+                <c:ptCount val="12176"/>
                 <c:pt idx="0">
                   <c:v>42865</c:v>
                 </c:pt>
@@ -6820,16 +6820,112 @@
                 </c:pt>
                 <c:pt idx="2175">
                   <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="2176">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="2177">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="2178">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="2179">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2180">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="2181">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="2182">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2183">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="2184">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="2185">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="2186">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="2187">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="2188">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="2189">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="2190">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="2191">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="2192">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="2193">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="2194">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="2195">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="2196">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="2197">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="2198">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="2199">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="2200">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="2201">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="2202">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="2203">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="2204">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="2205">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="2206">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="2207">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lithium!$H$2:$H$2177</c:f>
+              <c:f>Lithium!$H$2:$H$12177</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="2176"/>
+                <c:ptCount val="12176"/>
                 <c:pt idx="0">
                   <c:v>136000</c:v>
                 </c:pt>
@@ -13357,6 +13453,102 @@
                 </c:pt>
                 <c:pt idx="2175">
                   <c:v>164500</c:v>
+                </c:pt>
+                <c:pt idx="2176">
+                  <c:v>171000</c:v>
+                </c:pt>
+                <c:pt idx="2177">
+                  <c:v>181500</c:v>
+                </c:pt>
+                <c:pt idx="2178">
+                  <c:v>172500</c:v>
+                </c:pt>
+                <c:pt idx="2179">
+                  <c:v>172000</c:v>
+                </c:pt>
+                <c:pt idx="2180">
+                  <c:v>168000</c:v>
+                </c:pt>
+                <c:pt idx="2181">
+                  <c:v>160500</c:v>
+                </c:pt>
+                <c:pt idx="2182">
+                  <c:v>155469</c:v>
+                </c:pt>
+                <c:pt idx="2183">
+                  <c:v>153469</c:v>
+                </c:pt>
+                <c:pt idx="2184">
+                  <c:v>153000</c:v>
+                </c:pt>
+                <c:pt idx="2185">
+                  <c:v>144000</c:v>
+                </c:pt>
+                <c:pt idx="2186">
+                  <c:v>134500</c:v>
+                </c:pt>
+                <c:pt idx="2187">
+                  <c:v>135500</c:v>
+                </c:pt>
+                <c:pt idx="2188">
+                  <c:v>136000</c:v>
+                </c:pt>
+                <c:pt idx="2189">
+                  <c:v>138000</c:v>
+                </c:pt>
+                <c:pt idx="2190">
+                  <c:v>142500</c:v>
+                </c:pt>
+                <c:pt idx="2191">
+                  <c:v>143750</c:v>
+                </c:pt>
+                <c:pt idx="2192">
+                  <c:v>152000</c:v>
+                </c:pt>
+                <c:pt idx="2193">
+                  <c:v>161750</c:v>
+                </c:pt>
+                <c:pt idx="2194">
+                  <c:v>173000</c:v>
+                </c:pt>
+                <c:pt idx="2195">
+                  <c:v>172000</c:v>
+                </c:pt>
+                <c:pt idx="2196">
+                  <c:v>172500</c:v>
+                </c:pt>
+                <c:pt idx="2197">
+                  <c:v>161000</c:v>
+                </c:pt>
+                <c:pt idx="2198">
+                  <c:v>154000</c:v>
+                </c:pt>
+                <c:pt idx="2199">
+                  <c:v>156000</c:v>
+                </c:pt>
+                <c:pt idx="2200">
+                  <c:v>155250</c:v>
+                </c:pt>
+                <c:pt idx="2201">
+                  <c:v>154750</c:v>
+                </c:pt>
+                <c:pt idx="2202">
+                  <c:v>158500</c:v>
+                </c:pt>
+                <c:pt idx="2203">
+                  <c:v>159000</c:v>
+                </c:pt>
+                <c:pt idx="2204">
+                  <c:v>158000</c:v>
+                </c:pt>
+                <c:pt idx="2205">
+                  <c:v>159000</c:v>
+                </c:pt>
+                <c:pt idx="2206">
+                  <c:v>156500</c:v>
+                </c:pt>
+                <c:pt idx="2207">
+                  <c:v>158000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14428,7 +14620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2203"/>
+  <dimension ref="A1:H2209"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.125" style="3" bestFit="1" customWidth="1"/>
@@ -59006,7 +59198,7 @@
       <c r="A2203" s="3">
         <v>46090</v>
       </c>
-      <c r="B2203" s="9">
+      <c r="B2203" s="3">
         <v>46090</v>
       </c>
       <c r="C2203" s="19">
@@ -59026,6 +59218,162 @@
       </c>
       <c r="H2203" s="10">
         <v>154750</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2204" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B2204" s="3">
+        <v>46091</v>
+      </c>
+      <c r="C2204" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2204" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2204" s="16">
+        <v>158500</v>
+      </c>
+      <c r="F2204" s="16">
+        <v>164000</v>
+      </c>
+      <c r="G2204" s="16">
+        <v>153000</v>
+      </c>
+      <c r="H2204" s="10">
+        <v>158500</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2205" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B2205" s="3">
+        <v>46092</v>
+      </c>
+      <c r="C2205" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2205" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2205" s="16">
+        <v>159000</v>
+      </c>
+      <c r="F2205" s="16">
+        <v>164000</v>
+      </c>
+      <c r="G2205" s="16">
+        <v>154000</v>
+      </c>
+      <c r="H2205" s="10">
+        <v>159000</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2206" s="3">
+        <v>46093</v>
+      </c>
+      <c r="B2206" s="3">
+        <v>46093</v>
+      </c>
+      <c r="C2206" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2206" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2206" s="16">
+        <v>158000</v>
+      </c>
+      <c r="F2206" s="16">
+        <v>162000</v>
+      </c>
+      <c r="G2206" s="16">
+        <v>154000</v>
+      </c>
+      <c r="H2206" s="10">
+        <v>158000</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2207" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B2207" s="3">
+        <v>46094</v>
+      </c>
+      <c r="C2207" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2207" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2207" s="16">
+        <v>159000</v>
+      </c>
+      <c r="F2207" s="16">
+        <v>163000</v>
+      </c>
+      <c r="G2207" s="16">
+        <v>155000</v>
+      </c>
+      <c r="H2207" s="10">
+        <v>159000</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2208" s="3">
+        <v>46097</v>
+      </c>
+      <c r="B2208" s="3">
+        <v>46097</v>
+      </c>
+      <c r="C2208" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2208" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2208" s="16">
+        <v>156500</v>
+      </c>
+      <c r="F2208" s="16">
+        <v>163000</v>
+      </c>
+      <c r="G2208" s="16">
+        <v>150000</v>
+      </c>
+      <c r="H2208" s="10">
+        <v>156500</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2209" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B2209" s="3">
+        <v>46098</v>
+      </c>
+      <c r="C2209" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2209" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2209" s="16">
+        <v>156469</v>
+      </c>
+      <c r="F2209" s="16">
+        <v>163000</v>
+      </c>
+      <c r="G2209" s="16">
+        <v>153000</v>
+      </c>
+      <c r="H2209" s="10">
+        <v>158000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EB4AD4-FB85-417D-B303-A5F00516E89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AA49C2-0A23-4BB4-A726-2841FDCF35BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6983,6 +6983,9 @@
                 <c:pt idx="2226">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="2227">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13672,6 +13675,9 @@
                 </c:pt>
                 <c:pt idx="2226">
                   <c:v>161500</c:v>
+                </c:pt>
+                <c:pt idx="2227">
+                  <c:v>166000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14746,7 +14752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2228"/>
+  <dimension ref="A1:H2229"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="3" bestFit="1" customWidth="1"/>
@@ -59994,6 +60000,32 @@
       </c>
       <c r="H2228" s="10">
         <v>161500</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2229" s="3">
+        <v>46127</v>
+      </c>
+      <c r="B2229" s="3">
+        <v>46127</v>
+      </c>
+      <c r="C2229" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2229" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2229" s="16">
+        <v>161516</v>
+      </c>
+      <c r="F2229" s="16">
+        <v>169000</v>
+      </c>
+      <c r="G2229" s="16">
+        <v>161484</v>
+      </c>
+      <c r="H2229" s="10">
+        <v>166000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1613EF62-6DB9-47DF-8EDD-F5FB9DA932E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA285119-DB30-453B-AEB9-613D2368E883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -298,10 +298,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Lithium!$B$2:$B$12170</c:f>
+              <c:f>Lithium!$B$2:$B$12168</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="12169"/>
+                <c:ptCount val="12167"/>
                 <c:pt idx="0">
                   <c:v>42865</c:v>
                 </c:pt>
@@ -6988,16 +6988,25 @@
                 </c:pt>
                 <c:pt idx="2228">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="2229">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="2230">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="2231">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lithium!$H$2:$H$12170</c:f>
+              <c:f>Lithium!$H$2:$H$12168</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="12169"/>
+                <c:ptCount val="12167"/>
                 <c:pt idx="0">
                   <c:v>136000</c:v>
                 </c:pt>
@@ -13684,6 +13693,15 @@
                 </c:pt>
                 <c:pt idx="2228">
                   <c:v>167500</c:v>
+                </c:pt>
+                <c:pt idx="2229">
+                  <c:v>169500</c:v>
+                </c:pt>
+                <c:pt idx="2230">
+                  <c:v>172500</c:v>
+                </c:pt>
+                <c:pt idx="2231">
+                  <c:v>172000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13712,11 +13730,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="46387"/>
-          <c:min val="42736"/>
+          <c:min val="45292"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="yyyy;@" sourceLinked="0"/>
+        <c:numFmt formatCode="yyyy/mm;@" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -13758,11 +13776,15 @@
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="6"/>
+        <c:majorTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
         <c:axId val="744925887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="200000"/>
+          <c:min val="40000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -13814,6 +13836,7 @@
         <c:crossAx val="1246183455"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="40000"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -14459,13 +14482,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>209549</xdr:rowOff>
+      <xdr:rowOff>213359</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14758,7 +14781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2230"/>
+  <dimension ref="A1:H2233"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="3" bestFit="1" customWidth="1"/>
@@ -60058,6 +60081,84 @@
       </c>
       <c r="H2230" s="10">
         <v>167500</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2231" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B2231" s="9">
+        <v>46129</v>
+      </c>
+      <c r="C2231" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2231" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2231" s="16">
+        <v>169500</v>
+      </c>
+      <c r="F2231" s="16">
+        <v>173000</v>
+      </c>
+      <c r="G2231" s="16">
+        <v>166000</v>
+      </c>
+      <c r="H2231" s="10">
+        <v>169500</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2232" s="3">
+        <v>46132</v>
+      </c>
+      <c r="B2232" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C2232" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2232" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2232" s="16">
+        <v>172500</v>
+      </c>
+      <c r="F2232" s="16">
+        <v>175000</v>
+      </c>
+      <c r="G2232" s="16">
+        <v>169466</v>
+      </c>
+      <c r="H2232" s="10">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2233" s="3">
+        <v>46133</v>
+      </c>
+      <c r="B2233" s="9">
+        <v>46133</v>
+      </c>
+      <c r="C2233" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2233" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2233" s="16">
+        <v>172483</v>
+      </c>
+      <c r="F2233" s="16">
+        <v>174000</v>
+      </c>
+      <c r="G2233" s="16">
+        <v>170000</v>
+      </c>
+      <c r="H2233" s="10">
+        <v>172000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA285119-DB30-453B-AEB9-613D2368E883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B166DA8-3E90-49D0-8E4E-F06E435D43CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2248" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6998,6 +6998,12 @@
                 <c:pt idx="2231">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="2232">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="2233">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13702,6 +13708,12 @@
                 </c:pt>
                 <c:pt idx="2231">
                   <c:v>172000</c:v>
+                </c:pt>
+                <c:pt idx="2232">
+                  <c:v>171000</c:v>
+                </c:pt>
+                <c:pt idx="2233">
+                  <c:v>173000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14781,7 +14793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2233"/>
+  <dimension ref="A1:H2235"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="3" bestFit="1" customWidth="1"/>
@@ -60159,6 +60171,58 @@
       </c>
       <c r="H2233" s="10">
         <v>172000</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2234" s="3">
+        <v>46134</v>
+      </c>
+      <c r="B2234" s="9">
+        <v>46134</v>
+      </c>
+      <c r="C2234" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2234" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2234" s="16">
+        <v>171000</v>
+      </c>
+      <c r="F2234" s="16">
+        <v>173000</v>
+      </c>
+      <c r="G2234" s="16">
+        <v>169000</v>
+      </c>
+      <c r="H2234" s="10">
+        <v>171000</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2235" s="3">
+        <v>46135</v>
+      </c>
+      <c r="B2235" s="9">
+        <v>46135</v>
+      </c>
+      <c r="C2235" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2235" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2235" s="16">
+        <v>171017</v>
+      </c>
+      <c r="F2235" s="16">
+        <v>176000</v>
+      </c>
+      <c r="G2235" s="16">
+        <v>170000</v>
+      </c>
+      <c r="H2235" s="10">
+        <v>173000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B166DA8-3E90-49D0-8E4E-F06E435D43CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF2FF85-940C-47BB-A975-C4BE5F0D2AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2248" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -298,10 +298,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Lithium!$B$2:$B$12168</c:f>
+              <c:f>Lithium!$B$2:$B$12166</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="12167"/>
+                <c:ptCount val="12165"/>
                 <c:pt idx="0">
                   <c:v>42865</c:v>
                 </c:pt>
@@ -7003,16 +7003,34 @@
                 </c:pt>
                 <c:pt idx="2233">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="2234">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="2235">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="2236">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="2237">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="2238">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="2239">
+                  <c:v>46143</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lithium!$H$2:$H$12168</c:f>
+              <c:f>Lithium!$H$2:$H$12166</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="12167"/>
+                <c:ptCount val="12165"/>
                 <c:pt idx="0">
                   <c:v>136000</c:v>
                 </c:pt>
@@ -13714,6 +13732,18 @@
                 </c:pt>
                 <c:pt idx="2233">
                   <c:v>173000</c:v>
+                </c:pt>
+                <c:pt idx="2234">
+                  <c:v>173000</c:v>
+                </c:pt>
+                <c:pt idx="2235">
+                  <c:v>176000</c:v>
+                </c:pt>
+                <c:pt idx="2236">
+                  <c:v>174500</c:v>
+                </c:pt>
+                <c:pt idx="2237">
+                  <c:v>174500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14793,7 +14823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2235"/>
+  <dimension ref="A1:H2241"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="3" bestFit="1" customWidth="1"/>
@@ -60223,6 +60253,138 @@
       </c>
       <c r="H2235" s="10">
         <v>173000</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2236" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B2236" s="9">
+        <v>46136</v>
+      </c>
+      <c r="C2236" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2236" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2236" s="16">
+        <v>173000</v>
+      </c>
+      <c r="F2236" s="16">
+        <v>175000</v>
+      </c>
+      <c r="G2236" s="16">
+        <v>171000</v>
+      </c>
+      <c r="H2236" s="10">
+        <v>173000</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2237" s="3">
+        <v>46139</v>
+      </c>
+      <c r="B2237" s="9">
+        <v>46139</v>
+      </c>
+      <c r="C2237" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2237" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2237" s="16">
+        <v>176000</v>
+      </c>
+      <c r="F2237" s="16">
+        <v>179000</v>
+      </c>
+      <c r="G2237" s="16">
+        <v>172965</v>
+      </c>
+      <c r="H2237" s="10">
+        <v>176000</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2238" s="3">
+        <v>46140</v>
+      </c>
+      <c r="B2238" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C2238" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2238" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2238" s="16">
+        <v>174500</v>
+      </c>
+      <c r="F2238" s="16">
+        <v>177000</v>
+      </c>
+      <c r="G2238" s="16">
+        <v>172000</v>
+      </c>
+      <c r="H2238" s="10">
+        <v>174500</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2239" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B2239" s="9">
+        <v>46141</v>
+      </c>
+      <c r="C2239" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2239" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2239" s="16">
+        <v>174483</v>
+      </c>
+      <c r="F2239" s="16">
+        <v>177000</v>
+      </c>
+      <c r="G2239" s="16">
+        <v>172000</v>
+      </c>
+      <c r="H2239" s="10">
+        <v>174500</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2240" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B2240" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C2240" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2240" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2241" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B2241" s="9">
+        <v>46143</v>
+      </c>
+      <c r="C2241" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2241" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF2FF85-940C-47BB-A975-C4BE5F0D2AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFE5A85-05D0-4BF9-A7F8-0EDD2E967D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -298,10 +298,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Lithium!$B$2:$B$12166</c:f>
+              <c:f>Lithium!$B$2:$B$12161</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="12165"/>
+                <c:ptCount val="12160"/>
                 <c:pt idx="0">
                   <c:v>42865</c:v>
                 </c:pt>
@@ -7020,17 +7020,23 @@
                   <c:v>46142</c:v>
                 </c:pt>
                 <c:pt idx="2239">
-                  <c:v>46143</c:v>
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="2240">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="2241">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lithium!$H$2:$H$12166</c:f>
+              <c:f>Lithium!$H$2:$H$12161</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="12165"/>
+                <c:ptCount val="12160"/>
                 <c:pt idx="0">
                   <c:v>136000</c:v>
                 </c:pt>
@@ -13744,6 +13750,18 @@
                 </c:pt>
                 <c:pt idx="2237">
                   <c:v>174500</c:v>
+                </c:pt>
+                <c:pt idx="2238">
+                  <c:v>177000</c:v>
+                </c:pt>
+                <c:pt idx="2239">
+                  <c:v>187500</c:v>
+                </c:pt>
+                <c:pt idx="2240">
+                  <c:v>190500</c:v>
+                </c:pt>
+                <c:pt idx="2241">
+                  <c:v>194000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14823,7 +14841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2241"/>
+  <dimension ref="A1:H2247"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="3" bestFit="1" customWidth="1"/>
@@ -60372,13 +60390,25 @@
       <c r="D2240" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2241" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2240" s="16">
+        <v>177000</v>
+      </c>
+      <c r="F2240" s="16">
+        <v>180000</v>
+      </c>
+      <c r="G2240" s="16">
+        <v>176000</v>
+      </c>
+      <c r="H2240" s="10">
+        <v>177000</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2241" s="3">
-        <v>46143</v>
+        <v>46148</v>
       </c>
       <c r="B2241" s="9">
-        <v>46143</v>
+        <v>46148</v>
       </c>
       <c r="C2241" s="19">
         <v>0.625</v>
@@ -60386,6 +60416,86 @@
       <c r="D2241" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="E2241" s="16">
+        <v>187500</v>
+      </c>
+      <c r="F2241" s="16">
+        <v>193000</v>
+      </c>
+      <c r="G2241" s="16">
+        <v>182000</v>
+      </c>
+      <c r="H2241" s="10">
+        <v>187500</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2242" s="3">
+        <v>46149</v>
+      </c>
+      <c r="B2242" s="9">
+        <v>46149</v>
+      </c>
+      <c r="C2242" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2242" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2242" s="16">
+        <v>190500</v>
+      </c>
+      <c r="F2242" s="16">
+        <v>195000</v>
+      </c>
+      <c r="G2242" s="16">
+        <v>186000</v>
+      </c>
+      <c r="H2242" s="10">
+        <v>190500</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2243" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B2243" s="9">
+        <v>46150</v>
+      </c>
+      <c r="C2243" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2243" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2243" s="16">
+        <v>190481</v>
+      </c>
+      <c r="F2243" s="16">
+        <v>198000</v>
+      </c>
+      <c r="G2243" s="16">
+        <v>190000</v>
+      </c>
+      <c r="H2243" s="10">
+        <v>194000</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C2244" s="19"/>
+      <c r="D2244" s="4"/>
+    </row>
+    <row r="2245" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C2245" s="19"/>
+      <c r="D2245" s="4"/>
+    </row>
+    <row r="2246" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C2246" s="19"/>
+      <c r="D2246" s="4"/>
+    </row>
+    <row r="2247" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C2247" s="19"/>
+      <c r="D2247" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFE5A85-05D0-4BF9-A7F8-0EDD2E967D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B8864E-C7C6-4D99-81A5-BE4208FC206F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7028,6 +7028,12 @@
                 <c:pt idx="2241">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="2242">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="2243">
+                  <c:v>46154</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13762,6 +13768,12 @@
                 </c:pt>
                 <c:pt idx="2241">
                   <c:v>194000</c:v>
+                </c:pt>
+                <c:pt idx="2242">
+                  <c:v>195250</c:v>
+                </c:pt>
+                <c:pt idx="2243">
+                  <c:v>200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -60482,12 +60494,56 @@
       </c>
     </row>
     <row r="2244" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C2244" s="19"/>
-      <c r="D2244" s="4"/>
+      <c r="A2244" s="3">
+        <v>46153</v>
+      </c>
+      <c r="B2244" s="9">
+        <v>46153</v>
+      </c>
+      <c r="C2244" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2244" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2244" s="16">
+        <v>195250</v>
+      </c>
+      <c r="F2244" s="16">
+        <v>199000</v>
+      </c>
+      <c r="G2244" s="16">
+        <v>191500</v>
+      </c>
+      <c r="H2244" s="10">
+        <v>195250</v>
+      </c>
     </row>
     <row r="2245" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C2245" s="19"/>
-      <c r="D2245" s="4"/>
+      <c r="A2245" s="3">
+        <v>46154</v>
+      </c>
+      <c r="B2245" s="9">
+        <v>46154</v>
+      </c>
+      <c r="C2245" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2245" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2245" s="16">
+        <v>195270</v>
+      </c>
+      <c r="F2245" s="16">
+        <v>203000</v>
+      </c>
+      <c r="G2245" s="16">
+        <v>195211</v>
+      </c>
+      <c r="H2245" s="10">
+        <v>200000</v>
+      </c>
     </row>
     <row r="2246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C2246" s="19"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B8864E-C7C6-4D99-81A5-BE4208FC206F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAAF8DD-FC08-4DB5-8633-21F9B2A715C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7034,6 +7034,9 @@
                 <c:pt idx="2243">
                   <c:v>46154</c:v>
                 </c:pt>
+                <c:pt idx="2244">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13774,6 +13777,9 @@
                 </c:pt>
                 <c:pt idx="2243">
                   <c:v>200000</c:v>
+                </c:pt>
+                <c:pt idx="2244">
+                  <c:v>200500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -60546,8 +60552,30 @@
       </c>
     </row>
     <row r="2246" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C2246" s="19"/>
-      <c r="D2246" s="4"/>
+      <c r="A2246" s="3">
+        <v>46155</v>
+      </c>
+      <c r="B2246" s="9">
+        <v>46155</v>
+      </c>
+      <c r="C2246" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2246" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2246" s="16">
+        <v>199960</v>
+      </c>
+      <c r="F2246" s="16">
+        <v>203000</v>
+      </c>
+      <c r="G2246" s="16">
+        <v>198000</v>
+      </c>
+      <c r="H2246" s="10">
+        <v>200500</v>
+      </c>
     </row>
     <row r="2247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C2247" s="19"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAAF8DD-FC08-4DB5-8633-21F9B2A715C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B034829-7742-479C-9E2F-3B8AB0294001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7037,6 +7037,12 @@
                 <c:pt idx="2244">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="2245">
+                  <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="2246">
+                  <c:v>46157</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13780,6 +13786,12 @@
                 </c:pt>
                 <c:pt idx="2244">
                   <c:v>200500</c:v>
+                </c:pt>
+                <c:pt idx="2245">
+                  <c:v>195000</c:v>
+                </c:pt>
+                <c:pt idx="2246">
+                  <c:v>192000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14859,7 +14871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2247"/>
+  <dimension ref="A1:H2248"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="3" bestFit="1" customWidth="1"/>
@@ -60578,8 +60590,56 @@
       </c>
     </row>
     <row r="2247" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C2247" s="19"/>
-      <c r="D2247" s="4"/>
+      <c r="A2247" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B2247" s="9">
+        <v>46156</v>
+      </c>
+      <c r="C2247" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2247" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2247" s="16">
+        <v>165000</v>
+      </c>
+      <c r="F2247" s="16">
+        <v>200540</v>
+      </c>
+      <c r="G2247" s="16">
+        <v>191000</v>
+      </c>
+      <c r="H2247" s="10">
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2248" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B2248" s="9">
+        <v>46157</v>
+      </c>
+      <c r="C2248" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2248" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2248" s="16">
+        <v>194961</v>
+      </c>
+      <c r="F2248" s="16">
+        <v>196000</v>
+      </c>
+      <c r="G2248" s="16">
+        <v>188000</v>
+      </c>
+      <c r="H2248" s="10">
+        <v>192000</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24921444-978A-4DDA-AE56-A35C6B97F111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A6BC1F-CA06-48A1-BC70-9C6F9209AA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7046,6 +7046,9 @@
                 <c:pt idx="2247">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="2248">
+                  <c:v>46161</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13798,6 +13801,9 @@
                 </c:pt>
                 <c:pt idx="2247">
                   <c:v>191500</c:v>
+                </c:pt>
+                <c:pt idx="2248">
+                  <c:v>186500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14877,7 +14883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2249"/>
+  <dimension ref="A1:H2250"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -60671,6 +60677,32 @@
       </c>
       <c r="H2249" s="10">
         <v>191500</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:8">
+      <c r="A2250" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B2250" s="9">
+        <v>46161</v>
+      </c>
+      <c r="C2250" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2250" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2250" s="16">
+        <v>191481</v>
+      </c>
+      <c r="F2250" s="16">
+        <v>192000</v>
+      </c>
+      <c r="G2250" s="16">
+        <v>181000</v>
+      </c>
+      <c r="H2250" s="10">
+        <v>186500</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A6BC1F-CA06-48A1-BC70-9C6F9209AA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD86C80-3DFB-4295-98F2-867BE0B583EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7049,6 +7049,9 @@
                 <c:pt idx="2248">
                   <c:v>46161</c:v>
                 </c:pt>
+                <c:pt idx="2249">
+                  <c:v>46162</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13804,6 +13807,9 @@
                 </c:pt>
                 <c:pt idx="2248">
                   <c:v>186500</c:v>
+                </c:pt>
+                <c:pt idx="2249">
+                  <c:v>179000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14883,7 +14889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2250"/>
+  <dimension ref="A1:H2251"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -60703,6 +60709,32 @@
       </c>
       <c r="H2250" s="10">
         <v>186500</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:8">
+      <c r="A2251" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B2251" s="3">
+        <v>46162</v>
+      </c>
+      <c r="C2251" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2251" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2251" s="16">
+        <v>186481</v>
+      </c>
+      <c r="F2251" s="16">
+        <v>186519</v>
+      </c>
+      <c r="G2251" s="16">
+        <v>174000</v>
+      </c>
+      <c r="H2251" s="10">
+        <v>179000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96951D5B-2FC1-48B6-AA08-A0F827D80B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E011A9D8-FD09-41B1-B4B3-DF26481A1E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7058,6 +7058,9 @@
                 <c:pt idx="2251">
                   <c:v>46164</c:v>
                 </c:pt>
+                <c:pt idx="2252">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13822,6 +13825,9 @@
                 </c:pt>
                 <c:pt idx="2251">
                   <c:v>178000</c:v>
+                </c:pt>
+                <c:pt idx="2252">
+                  <c:v>183250</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14901,7 +14907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2253"/>
+  <dimension ref="A1:H2254"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
@@ -60799,6 +60805,32 @@
       </c>
       <c r="H2253" s="10">
         <v>178000</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:8">
+      <c r="A2254" s="3">
+        <v>46167</v>
+      </c>
+      <c r="B2254" s="9">
+        <v>46167</v>
+      </c>
+      <c r="C2254" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2254" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2254" s="16">
+        <v>177982</v>
+      </c>
+      <c r="F2254" s="16">
+        <v>185500</v>
+      </c>
+      <c r="G2254" s="16">
+        <v>177964</v>
+      </c>
+      <c r="H2254" s="10">
+        <v>183250</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6D78D3-185D-4269-986D-2E8C5803DED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2B524C-54C1-40A6-8812-B3AC3716C68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -241,9 +241,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -261,7 +261,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7067,6 +7067,9 @@
                 <c:pt idx="2254">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="2255">
+                  <c:v>46170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13840,6 +13843,9 @@
                 </c:pt>
                 <c:pt idx="2254">
                   <c:v>177000</c:v>
+                </c:pt>
+                <c:pt idx="2255">
+                  <c:v>175500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14919,15 +14925,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2256"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:H2257"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="11" customWidth="1"/>
-    <col min="5" max="7" width="11.5546875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="11" customWidth="1"/>
+    <col min="5" max="7" width="11.54296875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -60895,6 +60901,32 @@
       </c>
       <c r="H2256" s="10">
         <v>177000</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:8">
+      <c r="A2257" s="3">
+        <v>46170</v>
+      </c>
+      <c r="B2257" s="9">
+        <v>46170</v>
+      </c>
+      <c r="C2257" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2257" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2257" s="16">
+        <v>177018</v>
+      </c>
+      <c r="F2257" s="16">
+        <v>180000</v>
+      </c>
+      <c r="G2257" s="16">
+        <v>171000</v>
+      </c>
+      <c r="H2257" s="10">
+        <v>175500</v>
       </c>
     </row>
   </sheetData>
@@ -60907,9 +60939,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8FA39-E640-4E6A-B261-45B6002B9973}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -60949,7 +60981,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C1D3-27CA-4F31-B658-DBB84930A46D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3998CDE-A840-4155-BE29-5F4E6EF60E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27AD94C-43A7-433C-974B-151ED52E735F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -241,9 +241,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -261,7 +261,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7073,6 +7073,9 @@
                 <c:pt idx="2256">
                   <c:v>46171</c:v>
                 </c:pt>
+                <c:pt idx="2257">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13852,6 +13855,9 @@
                 </c:pt>
                 <c:pt idx="2256">
                   <c:v>177500</c:v>
+                </c:pt>
+                <c:pt idx="2257">
+                  <c:v>179000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14931,15 +14937,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2258"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H2259"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="11" customWidth="1"/>
-    <col min="5" max="7" width="11.54296875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="11" customWidth="1"/>
+    <col min="5" max="7" width="11.5546875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -60959,6 +60965,32 @@
       </c>
       <c r="H2258" s="10">
         <v>177500</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:8">
+      <c r="A2259" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B2259" s="9">
+        <v>46174</v>
+      </c>
+      <c r="C2259" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2259" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2259" s="16">
+        <v>177465</v>
+      </c>
+      <c r="F2259" s="16">
+        <v>182000</v>
+      </c>
+      <c r="G2259" s="16">
+        <v>176000</v>
+      </c>
+      <c r="H2259" s="10">
+        <v>179000</v>
       </c>
     </row>
   </sheetData>
@@ -60971,9 +61003,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8FA39-E640-4E6A-B261-45B6002B9973}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -61013,7 +61045,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C1D3-27CA-4F31-B658-DBB84930A46D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27AD94C-43A7-433C-974B-151ED52E735F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE3D593-AE88-491A-81D1-43D8A151AA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="17280" windowHeight="10690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -241,9 +241,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -261,7 +261,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7076,6 +7076,12 @@
                 <c:pt idx="2257">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="2258">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="2259">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13858,6 +13864,12 @@
                 </c:pt>
                 <c:pt idx="2257">
                   <c:v>179000</c:v>
+                </c:pt>
+                <c:pt idx="2258">
+                  <c:v>175750</c:v>
+                </c:pt>
+                <c:pt idx="2259">
+                  <c:v>170500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14937,15 +14949,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2259"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:H2261"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="11" customWidth="1"/>
-    <col min="5" max="7" width="11.5546875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="11" customWidth="1"/>
+    <col min="5" max="7" width="11.54296875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -60991,6 +61003,58 @@
       </c>
       <c r="H2259" s="10">
         <v>179000</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:8">
+      <c r="A2260" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B2260" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C2260" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2260" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2260" s="16">
+        <v>175750</v>
+      </c>
+      <c r="F2260" s="16">
+        <v>180000</v>
+      </c>
+      <c r="G2260" s="16">
+        <v>171500</v>
+      </c>
+      <c r="H2260" s="10">
+        <v>175750</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:8">
+      <c r="A2261" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B2261" s="9">
+        <v>46176</v>
+      </c>
+      <c r="C2261" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2261" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2261" s="16">
+        <v>175715</v>
+      </c>
+      <c r="F2261" s="16">
+        <v>175785</v>
+      </c>
+      <c r="G2261" s="16">
+        <v>166000</v>
+      </c>
+      <c r="H2261" s="10">
+        <v>170500</v>
       </c>
     </row>
   </sheetData>
@@ -61003,9 +61067,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8FA39-E640-4E6A-B261-45B6002B9973}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -61045,7 +61109,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C1D3-27CA-4F31-B658-DBB84930A46D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BDF412-4116-4521-9177-9CBC12CCD82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218F3DEE-B27E-4491-8335-2C04F0B10ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7088,6 +7088,9 @@
                 <c:pt idx="2261">
                   <c:v>46178</c:v>
                 </c:pt>
+                <c:pt idx="2262">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13882,6 +13885,9 @@
                 </c:pt>
                 <c:pt idx="2261">
                   <c:v>163000</c:v>
+                </c:pt>
+                <c:pt idx="2262">
+                  <c:v>163750</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14961,7 +14967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2263"/>
+  <dimension ref="A1:H2264"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -61119,6 +61125,32 @@
       </c>
       <c r="H2263" s="10">
         <v>163000</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:8">
+      <c r="A2264" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B2264" s="9">
+        <v>46181</v>
+      </c>
+      <c r="C2264" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2264" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2264" s="16">
+        <v>162984</v>
+      </c>
+      <c r="F2264" s="16">
+        <v>165500</v>
+      </c>
+      <c r="G2264" s="16">
+        <v>162000</v>
+      </c>
+      <c r="H2264" s="10">
+        <v>163750</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1949CB9-24FF-4147-B943-61C2ADE4EE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10A5D95-4BD8-481F-96A6-A8A2F2AF57D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -237,9 +237,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -257,7 +257,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7093,6 +7093,9 @@
                 <c:pt idx="2264">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="2265">
+                  <c:v>46184</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13896,6 +13899,9 @@
                 </c:pt>
                 <c:pt idx="2264">
                   <c:v>165750</c:v>
+                </c:pt>
+                <c:pt idx="2265">
+                  <c:v>166500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14975,15 +14981,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2266"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H2267"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="11" customWidth="1"/>
-    <col min="5" max="7" width="11.54296875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="11" customWidth="1"/>
+    <col min="5" max="7" width="11.5546875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -61211,6 +61217,32 @@
       </c>
       <c r="H2266" s="10">
         <v>165750</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:8">
+      <c r="A2267" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B2267" s="9">
+        <v>46184</v>
+      </c>
+      <c r="C2267" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2267" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2267" s="16">
+        <v>165717</v>
+      </c>
+      <c r="F2267" s="16">
+        <v>169000</v>
+      </c>
+      <c r="G2267" s="16">
+        <v>164000</v>
+      </c>
+      <c r="H2267" s="10">
+        <v>166500</v>
       </c>
     </row>
   </sheetData>
@@ -61223,9 +61255,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8FA39-E640-4E6A-B261-45B6002B9973}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -61265,7 +61297,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C1D3-27CA-4F31-B658-DBB84930A46D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
